--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487673_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487673_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>I. BLANCO-ARGIBAY GONZALEZ</t>
+          <t>J. VILASANCHEZ FREIJOMIL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9315</v>
+        <v>0.1053</v>
       </c>
       <c r="E2" t="n">
-        <v>2.4305</v>
+        <v>1.4528</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.499</v>
+        <v>-1.3475</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.9596</v>
+        <v>-1.2055</v>
       </c>
       <c r="H2" t="n">
-        <v>-1.221</v>
+        <v>-0.8346</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2614</v>
+        <v>-0.3709</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.0494</v>
+        <v>0.366</v>
       </c>
       <c r="K2" t="n">
-        <v>0.6179</v>
+        <v>0.9928</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.6673</v>
+        <v>-0.6267</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.9102</v>
+        <v>-1.5716</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.8389</v>
+        <v>-1.8274</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9287</v>
+        <v>0.2558</v>
       </c>
       <c r="P2" t="n">
-        <v>0.5821</v>
+        <v>0.194</v>
       </c>
       <c r="Q2" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R2" t="n">
-        <v>1.5523</v>
+        <v>1.1642</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2985</v>
+        <v>0.8347</v>
       </c>
       <c r="T2" t="n">
-        <v>1.9919</v>
+        <v>0.5508999999999999</v>
       </c>
       <c r="U2" t="n">
-        <v>0.3067</v>
+        <v>0.2838</v>
       </c>
       <c r="V2" t="n">
-        <v>-0.9896</v>
+        <v>0.2821</v>
       </c>
       <c r="W2" t="n">
-        <v>1.4582</v>
+        <v>1.506</v>
       </c>
       <c r="X2" t="n">
-        <v>-2.4477</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. VILASANCHEZ FREIJOMIL</t>
+          <t>I. BLANCO-ARGIBAY GONZALEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.2673</v>
+        <v>-0.7241</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3527</v>
+        <v>1.1292</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.62</v>
+        <v>-1.8533</v>
       </c>
       <c r="G3" t="n">
-        <v>-1.2055</v>
+        <v>-0.9596</v>
       </c>
       <c r="H3" t="n">
-        <v>-0.8346</v>
+        <v>-1.221</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.3709</v>
+        <v>0.2614</v>
       </c>
       <c r="J3" t="n">
-        <v>0.366</v>
+        <v>-0.0494</v>
       </c>
       <c r="K3" t="n">
-        <v>0.9928</v>
+        <v>0.6179</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.6267</v>
+        <v>-0.6673</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.5716</v>
+        <v>-0.9102</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.8274</v>
+        <v>-1.8389</v>
       </c>
       <c r="O3" t="n">
-        <v>0.2558</v>
+        <v>0.9287</v>
       </c>
       <c r="P3" t="n">
-        <v>0.194</v>
+        <v>0.5821</v>
       </c>
       <c r="Q3" t="n">
         <v>-0.9702</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1642</v>
+        <v>1.5523</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4621</v>
+        <v>0.6429</v>
       </c>
       <c r="T3" t="n">
-        <v>0.4508</v>
+        <v>0.6906</v>
       </c>
       <c r="U3" t="n">
-        <v>0.0112</v>
+        <v>-0.0476</v>
       </c>
       <c r="V3" t="n">
-        <v>0.2821</v>
+        <v>-0.9896</v>
       </c>
       <c r="W3" t="n">
-        <v>1.506</v>
+        <v>1.4582</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.2239</v>
+        <v>-2.4477</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.3882</v>
+        <v>-1.4794</v>
       </c>
       <c r="E4" t="n">
-        <v>-3.5617</v>
+        <v>-3.7619</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1734</v>
+        <v>2.2824</v>
       </c>
       <c r="G4" t="n">
         <v>-3.0549</v>
@@ -766,13 +766,13 @@
         <v>1.5523</v>
       </c>
       <c r="S4" t="n">
-        <v>0.4248</v>
+        <v>0.3337</v>
       </c>
       <c r="T4" t="n">
-        <v>0.3544</v>
+        <v>0.1542</v>
       </c>
       <c r="U4" t="n">
-        <v>0.07049999999999999</v>
+        <v>0.1795</v>
       </c>
       <c r="V4" t="n">
         <v>0.6597</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. CUESTA DE SANTOS</t>
+          <t>E. BOADA MONTESDEOCA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.8286</v>
+        <v>-1.9942</v>
       </c>
       <c r="E5" t="n">
-        <v>-3.1493</v>
+        <v>-2.0757</v>
       </c>
       <c r="F5" t="n">
-        <v>1.3207</v>
+        <v>0.0815</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.7987</v>
+        <v>1.4492</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.9812</v>
+        <v>1.3157</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8175</v>
+        <v>0.1335</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.4953</v>
+        <v>1.6519</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.1606</v>
+        <v>2.3192</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.3347</v>
+        <v>-0.6673</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.3034</v>
+        <v>-0.2027</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.8206</v>
+        <v>-1.0035</v>
       </c>
       <c r="O5" t="n">
-        <v>0.5172</v>
+        <v>0.8008</v>
       </c>
       <c r="P5" t="n">
-        <v>-1.5523</v>
+        <v>-2.3284</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.9105</v>
+        <v>-3.8806</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3582</v>
+        <v>1.5523</v>
       </c>
       <c r="S5" t="n">
-        <v>2.1821</v>
+        <v>-0.221</v>
       </c>
       <c r="T5" t="n">
-        <v>1.0699</v>
+        <v>0.1531</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1122</v>
+        <v>-0.374</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.6597</v>
+        <v>-0.894</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1865</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.8462</v>
+        <v>-0.894</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>E. BOADA MONTESDEOCA</t>
+          <t>A. GOMEZ SERRANO</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-2.0938</v>
+        <v>-2.7117</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.8755</v>
+        <v>-2.2497</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.2183</v>
+        <v>-0.462</v>
       </c>
       <c r="G6" t="n">
-        <v>1.4492</v>
+        <v>-2.2998</v>
       </c>
       <c r="H6" t="n">
-        <v>1.3157</v>
+        <v>-2.4906</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1335</v>
+        <v>0.1908</v>
       </c>
       <c r="J6" t="n">
-        <v>1.6519</v>
+        <v>-1.3078</v>
       </c>
       <c r="K6" t="n">
-        <v>2.3192</v>
+        <v>-1.2317</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.6673</v>
+        <v>-0.0762</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.2027</v>
+        <v>-0.992</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.0035</v>
+        <v>-1.2589</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8008</v>
+        <v>0.2669</v>
       </c>
       <c r="P6" t="n">
-        <v>-2.3284</v>
+        <v>-0.194</v>
       </c>
       <c r="Q6" t="n">
-        <v>-3.8806</v>
+        <v>-0.9702</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5523</v>
+        <v>0.7761</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3206</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="T6" t="n">
-        <v>0.3533</v>
+        <v>0.0283</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.6738</v>
+        <v>0.0359</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.894</v>
+        <v>-0.2821</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.894</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A. GOMEZ SERRANO</t>
+          <t>C. CUESTA DE SANTOS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-2.4114</v>
+        <v>-2.8286</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.9494</v>
+        <v>-3.5497</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.462</v>
+        <v>0.7211</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.2998</v>
+        <v>-1.7987</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.4906</v>
+        <v>-0.9812</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1908</v>
+        <v>-0.8175</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.3078</v>
+        <v>-1.4953</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.2317</v>
+        <v>-0.1606</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.0762</v>
+        <v>-1.3347</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.992</v>
+        <v>-0.3034</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.2589</v>
+        <v>-0.8206</v>
       </c>
       <c r="O7" t="n">
-        <v>0.2669</v>
+        <v>0.5172</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.194</v>
+        <v>-1.5523</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9702</v>
+        <v>-2.9105</v>
       </c>
       <c r="R7" t="n">
-        <v>0.7761</v>
+        <v>1.3582</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3645</v>
+        <v>1.1821</v>
       </c>
       <c r="T7" t="n">
-        <v>0.3286</v>
+        <v>0.6695</v>
       </c>
       <c r="U7" t="n">
-        <v>0.0359</v>
+        <v>0.5125999999999999</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.2821</v>
+        <v>-0.6597</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.1865</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2821</v>
+        <v>-0.8462</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-5.8645</v>
+        <v>-5.0816</v>
       </c>
       <c r="E8" t="n">
-        <v>-5.2219</v>
+        <v>-4.2209</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.6425999999999999</v>
+        <v>-0.8606</v>
       </c>
       <c r="G8" t="n">
         <v>-2.0414</v>
@@ -1078,13 +1078,13 @@
         <v>0.5821</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.1947</v>
+        <v>0.5883</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9567</v>
+        <v>0.0443</v>
       </c>
       <c r="U8" t="n">
-        <v>0.762</v>
+        <v>0.544</v>
       </c>
       <c r="V8" t="n">
         <v>-0.3299</v>
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-8.4567</v>
+        <v>-6.6648</v>
       </c>
       <c r="E9" t="n">
-        <v>-7.524</v>
+        <v>-6.2228</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.9327</v>
+        <v>-0.4421</v>
       </c>
       <c r="G9" t="n">
         <v>-7.7262</v>
@@ -1156,13 +1156,13 @@
         <v>2.1344</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.8185</v>
+        <v>-0.0266</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.2708</v>
+        <v>0.0305</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5477</v>
+        <v>-0.0572</v>
       </c>
       <c r="V9" t="n">
         <v>0.894</v>
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-21.379</v>
+        <v>-21.3791</v>
       </c>
       <c r="E10" t="n">
-        <v>-19.4986</v>
+        <v>-19.4987</v>
       </c>
       <c r="F10" t="n">
         <v>-1.8805</v>
@@ -1210,7 +1210,7 @@
         <v>-11.16</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.5105999999999997</v>
+        <v>-0.5106000000000002</v>
       </c>
       <c r="L10" t="n">
         <v>-10.6494</v>
@@ -1234,7 +1234,7 @@
         <v>10.6719</v>
       </c>
       <c r="S10" t="n">
-        <v>3.3982</v>
+        <v>3.3983</v>
       </c>
       <c r="T10" t="n">
         <v>2.3214</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>6.4262</v>
+        <v>6.939</v>
       </c>
       <c r="E11" t="n">
-        <v>3.8471</v>
+        <v>3.747</v>
       </c>
       <c r="F11" t="n">
-        <v>2.5792</v>
+        <v>3.192</v>
       </c>
       <c r="G11" t="n">
         <v>2.3661</v>
@@ -1312,13 +1312,13 @@
         <v>1.9403</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3279</v>
+        <v>0.1848</v>
       </c>
       <c r="T11" t="n">
-        <v>0.1962</v>
+        <v>0.0961</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5242</v>
+        <v>0.0886</v>
       </c>
       <c r="V11" t="n">
         <v>2.4477</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>5.4192</v>
+        <v>6.893</v>
       </c>
       <c r="E12" t="n">
-        <v>2.0396</v>
+        <v>2.8404</v>
       </c>
       <c r="F12" t="n">
-        <v>3.3796</v>
+        <v>4.0526</v>
       </c>
       <c r="G12" t="n">
         <v>5.609</v>
@@ -1390,13 +1390,13 @@
         <v>2.5224</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.6375</v>
+        <v>-0.1637</v>
       </c>
       <c r="T12" t="n">
-        <v>-1.393</v>
+        <v>-0.5921999999999999</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2445</v>
+        <v>0.4285</v>
       </c>
       <c r="V12" t="n">
         <v>1.8358</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.0945</v>
+        <v>5.7045</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9325</v>
+        <v>2.7333</v>
       </c>
       <c r="F13" t="n">
-        <v>2.162</v>
+        <v>2.9712</v>
       </c>
       <c r="G13" t="n">
         <v>4.4248</v>
@@ -1468,13 +1468,13 @@
         <v>2.1344</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.7766</v>
+        <v>-0.1666</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.1508</v>
+        <v>-0.35</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.6258</v>
+        <v>0.1834</v>
       </c>
       <c r="V13" t="n">
         <v>0.2821</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.0442</v>
+        <v>4.3934</v>
       </c>
       <c r="E14" t="n">
-        <v>1.0591</v>
+        <v>1.3594</v>
       </c>
       <c r="F14" t="n">
-        <v>2.9851</v>
+        <v>3.034</v>
       </c>
       <c r="G14" t="n">
         <v>2.6346</v>
@@ -1546,13 +1546,13 @@
         <v>1.1642</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.668</v>
+        <v>-0.3188</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5328000000000001</v>
+        <v>-0.2325</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.1352</v>
+        <v>-0.0863</v>
       </c>
       <c r="V14" t="n">
         <v>1.8836</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.8051</v>
+        <v>0.7891</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.8173</v>
+        <v>-2.0185</v>
       </c>
       <c r="F15" t="n">
-        <v>2.6224</v>
+        <v>2.8076</v>
       </c>
       <c r="G15" t="n">
         <v>0.8080000000000001</v>
@@ -1624,13 +1624,13 @@
         <v>2.5224</v>
       </c>
       <c r="S15" t="n">
-        <v>1.3284</v>
+        <v>0.3124</v>
       </c>
       <c r="T15" t="n">
-        <v>1.3369</v>
+        <v>0.1357</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.008500000000000001</v>
+        <v>0.1767</v>
       </c>
       <c r="V15" t="n">
         <v>-1.8836</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. VAZQUEZ JEREZ</t>
+          <t>A. VIDAL RODRIGUEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1156</v>
+        <v>0.6423</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.6136</v>
+        <v>-0.1128</v>
       </c>
       <c r="F16" t="n">
-        <v>1.7291</v>
+        <v>0.755</v>
       </c>
       <c r="G16" t="n">
-        <v>1.2432</v>
+        <v>1.5095</v>
       </c>
       <c r="H16" t="n">
-        <v>1.1097</v>
+        <v>0.9351</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1335</v>
+        <v>0.5745</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0834</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="K16" t="n">
-        <v>1.7507</v>
+        <v>0.6797</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.6673</v>
+        <v>0.0406</v>
       </c>
       <c r="M16" t="n">
-        <v>0.1598</v>
+        <v>0.7893</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.641</v>
+        <v>0.2554</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8008</v>
+        <v>0.5339</v>
       </c>
       <c r="P16" t="n">
-        <v>-0.5821</v>
+        <v>-0.3881</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R16" t="n">
-        <v>1.3582</v>
+        <v>0.5821</v>
       </c>
       <c r="S16" t="n">
-        <v>1.0664</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2434</v>
+        <v>0.1371</v>
       </c>
       <c r="U16" t="n">
-        <v>0.823</v>
+        <v>-0.0521</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6119</v>
+        <v>-0.5642</v>
       </c>
       <c r="W16" t="n">
         <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.6119</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. VIDAL RODRIGUEZ</t>
+          <t>D. VAZQUEZ JEREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6484</v>
+        <v>0.6128</v>
       </c>
       <c r="E17" t="n">
-        <v>0.1875</v>
+        <v>-0.8138</v>
       </c>
       <c r="F17" t="n">
-        <v>0.4609</v>
+        <v>1.4265</v>
       </c>
       <c r="G17" t="n">
-        <v>1.5095</v>
+        <v>1.2432</v>
       </c>
       <c r="H17" t="n">
-        <v>0.9351</v>
+        <v>1.1097</v>
       </c>
       <c r="I17" t="n">
-        <v>0.5745</v>
+        <v>0.1335</v>
       </c>
       <c r="J17" t="n">
-        <v>0.7203000000000001</v>
+        <v>1.0834</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6797</v>
+        <v>1.7507</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0406</v>
+        <v>-0.6673</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7893</v>
+        <v>0.1598</v>
       </c>
       <c r="N17" t="n">
-        <v>0.2554</v>
+        <v>-0.641</v>
       </c>
       <c r="O17" t="n">
-        <v>0.5339</v>
+        <v>0.8008</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.3881</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q17" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R17" t="n">
-        <v>0.5821</v>
+        <v>1.3582</v>
       </c>
       <c r="S17" t="n">
-        <v>0.0911</v>
+        <v>0.5636</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4374</v>
+        <v>0.0432</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3463</v>
+        <v>0.5204</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.5642</v>
+        <v>-0.6119</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.5642</v>
+        <v>-0.6119</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. JIMENEZ HERNANDEZ</t>
+          <t>I. MENCARA JIMENEZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5705</v>
+        <v>0.3937</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.9402</v>
+        <v>-0.8364</v>
       </c>
       <c r="F18" t="n">
-        <v>2.5106</v>
+        <v>1.2301</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5443</v>
+        <v>-0.1214</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6163</v>
+        <v>0.4358</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.1606</v>
+        <v>-0.5572</v>
       </c>
       <c r="J18" t="n">
-        <v>-2.4392</v>
+        <v>-0.6645</v>
       </c>
       <c r="K18" t="n">
-        <v>0.1895</v>
+        <v>0.6879999999999999</v>
       </c>
       <c r="L18" t="n">
-        <v>-2.6287</v>
+        <v>-1.3524</v>
       </c>
       <c r="M18" t="n">
-        <v>1.8949</v>
+        <v>0.5431</v>
       </c>
       <c r="N18" t="n">
-        <v>0.4267</v>
+        <v>-0.2521</v>
       </c>
       <c r="O18" t="n">
-        <v>1.4681</v>
+        <v>0.7952</v>
       </c>
       <c r="P18" t="n">
+        <v>1.1642</v>
+      </c>
+      <c r="Q18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>-0.9702</v>
-      </c>
       <c r="R18" t="n">
-        <v>0.9702</v>
+        <v>1.1642</v>
       </c>
       <c r="S18" t="n">
-        <v>1.679</v>
+        <v>-0.6491</v>
       </c>
       <c r="T18" t="n">
-        <v>1.4692</v>
+        <v>-0.1719</v>
       </c>
       <c r="U18" t="n">
-        <v>0.2098</v>
+        <v>-0.4772</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.5642</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.5642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>I. MENCARA JIMENEZ</t>
+          <t>J. JIMENEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.5278</v>
+        <v>-0.0052</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.1367</v>
+        <v>-2.6408</v>
       </c>
       <c r="F19" t="n">
-        <v>0.6088</v>
+        <v>2.6357</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.1214</v>
+        <v>-0.5443</v>
       </c>
       <c r="H19" t="n">
-        <v>0.4358</v>
+        <v>0.6163</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.5572</v>
+        <v>-1.1606</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.6645</v>
+        <v>-2.4392</v>
       </c>
       <c r="K19" t="n">
-        <v>0.6879999999999999</v>
+        <v>0.1895</v>
       </c>
       <c r="L19" t="n">
-        <v>-1.3524</v>
+        <v>-2.6287</v>
       </c>
       <c r="M19" t="n">
-        <v>0.5431</v>
+        <v>1.8949</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.2521</v>
+        <v>0.4267</v>
       </c>
       <c r="O19" t="n">
-        <v>0.7952</v>
+        <v>1.4681</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1642</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1642</v>
+        <v>0.9702</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.5706</v>
+        <v>1.1034</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.4722</v>
+        <v>0.7685</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0985</v>
+        <v>0.3348</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>-0.5642</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.9922</v>
+        <v>-0.5495</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.5977</v>
+        <v>-2.3975</v>
       </c>
       <c r="F20" t="n">
-        <v>1.6056</v>
+        <v>1.8481</v>
       </c>
       <c r="G20" t="n">
         <v>-0.3947</v>
@@ -2014,13 +2014,13 @@
         <v>2.1344</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.4796</v>
+        <v>-1.0369</v>
       </c>
       <c r="T20" t="n">
-        <v>-1.0902</v>
+        <v>-0.89</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3894</v>
+        <v>-0.1469</v>
       </c>
       <c r="V20" t="n">
         <v>-0.2821</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2247</v>
+        <v>-1.0973</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0799</v>
+        <v>0.0202</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1447</v>
+        <v>-1.1175</v>
       </c>
       <c r="G21" t="n">
         <v>0.1022</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.103</v>
+        <v>0.0244</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1211</v>
+        <v>-0.021</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0182</v>
+        <v>0.0454</v>
       </c>
       <c r="V21" t="n">
         <v>-1.2239</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>21.379</v>
+        <v>24.7158</v>
       </c>
       <c r="E22" t="n">
-        <v>1.880399999999999</v>
+        <v>1.8805</v>
       </c>
       <c r="F22" t="n">
-        <v>19.4986</v>
+        <v>22.8353</v>
       </c>
       <c r="G22" t="n">
         <v>17.637</v>
@@ -2143,7 +2143,7 @@
         <v>6.729299999999999</v>
       </c>
       <c r="J22" t="n">
-        <v>6.477099999999998</v>
+        <v>6.4771</v>
       </c>
       <c r="K22" t="n">
         <v>10.3974</v>
@@ -2155,13 +2155,13 @@
         <v>11.1601</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5105</v>
+        <v>0.5105000000000002</v>
       </c>
       <c r="O22" t="n">
         <v>10.6495</v>
       </c>
       <c r="P22" t="n">
-        <v>5.8209</v>
+        <v>5.820900000000001</v>
       </c>
       <c r="Q22" t="n">
         <v>-10.672</v>
@@ -2170,13 +2170,13 @@
         <v>16.4928</v>
       </c>
       <c r="S22" t="n">
-        <v>-3.3983</v>
+        <v>-0.06149999999999986</v>
       </c>
       <c r="T22" t="n">
         <v>-1.077</v>
       </c>
       <c r="U22" t="n">
-        <v>-2.3214</v>
+        <v>1.0153</v>
       </c>
       <c r="V22" t="n">
         <v>1.319300000000001</v>
